--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123971382</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -911,6 +911,334 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123996244</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>507587</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706176</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123996283</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>507603</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706042</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123996214</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8447</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>507650</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706235</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123971382</v>
+        <v>123970525</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran O, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507440</v>
+        <v>507540</v>
       </c>
       <c r="R2" t="n">
-        <v>6706045</v>
+        <v>6706173</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123970525</v>
+        <v>123971382</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran O, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507540</v>
+        <v>507440</v>
       </c>
       <c r="R3" t="n">
-        <v>6706173</v>
+        <v>6706045</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +906,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996244</v>
+        <v>123996283</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507587</v>
+        <v>507603</v>
       </c>
       <c r="R4" t="n">
-        <v>6706176</v>
+        <v>6706042</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,6 +1000,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996283</v>
+        <v>123996244</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1031,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507603</v>
+        <v>507587</v>
       </c>
       <c r="R5" t="n">
-        <v>6706042</v>
+        <v>6706176</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1110,7 +1111,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123970525</v>
+        <v>123971382</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran O, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507540</v>
+        <v>507440</v>
       </c>
       <c r="R2" t="n">
-        <v>6706173</v>
+        <v>6706045</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +794,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123971382</v>
+        <v>123970525</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran O, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507440</v>
+        <v>507540</v>
       </c>
       <c r="R3" t="n">
-        <v>6706045</v>
+        <v>6706173</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1019,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996244</v>
+        <v>123996214</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,29 +1035,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1067,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507587</v>
+        <v>507650</v>
       </c>
       <c r="R5" t="n">
-        <v>6706176</v>
+        <v>6706235</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1111,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996214</v>
+        <v>123996244</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,30 +1147,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1178,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507650</v>
+        <v>507587</v>
       </c>
       <c r="R6" t="n">
-        <v>6706235</v>
+        <v>6706176</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1222,7 +1223,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123970525</v>
+        <v>123971382</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran O, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507540</v>
+        <v>507440</v>
       </c>
       <c r="R2" t="n">
-        <v>6706173</v>
+        <v>6706045</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +794,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123971382</v>
+        <v>123970525</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran O, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507440</v>
+        <v>507540</v>
       </c>
       <c r="R3" t="n">
-        <v>6706045</v>
+        <v>6706173</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +906,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996214</v>
+        <v>123996244</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,30 +929,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -962,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507650</v>
+        <v>507587</v>
       </c>
       <c r="R4" t="n">
-        <v>6706235</v>
+        <v>6706176</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1131,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996244</v>
+        <v>123996214</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,29 +1145,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1179,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507587</v>
+        <v>507650</v>
       </c>
       <c r="R6" t="n">
-        <v>6706176</v>
+        <v>6706235</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1223,6 +1222,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123971382</v>
+        <v>123970525</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran O, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507440</v>
+        <v>507540</v>
       </c>
       <c r="R2" t="n">
-        <v>6706045</v>
+        <v>6706173</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123970525</v>
+        <v>123971382</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran O, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507540</v>
+        <v>507440</v>
       </c>
       <c r="R3" t="n">
-        <v>6706173</v>
+        <v>6706045</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123970525</v>
+        <v>123971382</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran O, Dlr</t>
+          <t>Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507540</v>
+        <v>507440</v>
       </c>
       <c r="R2" t="n">
-        <v>6706173</v>
+        <v>6706045</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,17 +794,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123971382</v>
+        <v>123970525</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,50 +813,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyran, Dlr</t>
+          <t>Långmyran O, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507440</v>
+        <v>507540</v>
       </c>
       <c r="R3" t="n">
-        <v>6706045</v>
+        <v>6706173</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca.</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,17 +906,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996244</v>
+        <v>123996283</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,35 +925,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507587</v>
+        <v>507603</v>
       </c>
       <c r="R4" t="n">
-        <v>6706176</v>
+        <v>6706042</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,6 +1000,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996283</v>
+        <v>123996244</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1031,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507603</v>
+        <v>507587</v>
       </c>
       <c r="R5" t="n">
-        <v>6706042</v>
+        <v>6706176</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1110,7 +1111,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996283</v>
+        <v>123996214</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,30 +925,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507603</v>
+        <v>507650</v>
       </c>
       <c r="R4" t="n">
-        <v>6706042</v>
+        <v>6706235</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1129,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996214</v>
+        <v>123996283</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,36 +1147,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507650</v>
+        <v>507603</v>
       </c>
       <c r="R6" t="n">
-        <v>6706235</v>
+        <v>6706042</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>

--- a/artfynd/A 14597-2025 artfynd.xlsx
+++ b/artfynd/A 14597-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123996214</v>
+        <v>123996283</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,36 +925,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -962,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507650</v>
+        <v>507603</v>
       </c>
       <c r="R4" t="n">
-        <v>6706235</v>
+        <v>6706042</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1025,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123996244</v>
+        <v>123996214</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,29 +1035,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1073,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507587</v>
+        <v>507650</v>
       </c>
       <c r="R5" t="n">
-        <v>6706176</v>
+        <v>6706235</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,6 +1112,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123996283</v>
+        <v>123996244</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,30 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507603</v>
+        <v>507587</v>
       </c>
       <c r="R6" t="n">
-        <v>6706042</v>
+        <v>6706176</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1222,7 +1223,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
